--- a/Linear Regulator/Book1.xlsx
+++ b/Linear Regulator/Book1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoa-my.sharepoint.com/personal/qche619_uoa_auckland_ac_nz/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qche619\Downloads\ELECTENG-311-Teamwork\Linear Regulator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45BD6E63-2612-4E76-B0B0-9D973320905C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41D5467-8EBA-4764-B4C7-2A7C42B6BF3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D829F5A1-D388-437B-AA51-65B45AF8D5F5}"/>
   </bookViews>
@@ -512,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FE5874B-1229-449E-B35A-29CF6E1C6CD6}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="10.25" customWidth="1"/>
@@ -523,7 +523,7 @@
     <col min="7" max="7" width="24.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -546,7 +546,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="16.5">
+    <row r="2" spans="1:9" ht="16.5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -566,7 +566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3">
         <v>2</v>
       </c>
@@ -586,7 +586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="16.5">
+    <row r="4" spans="1:9" ht="16.5">
       <c r="A4">
         <v>3</v>
       </c>
@@ -606,7 +606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="16.5">
+    <row r="5" spans="1:9" ht="16.5">
       <c r="A5">
         <v>4</v>
       </c>
@@ -626,7 +626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="16.5">
+    <row r="6" spans="1:9" ht="16.5">
       <c r="A6">
         <v>5</v>
       </c>
@@ -646,7 +646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="16.5">
+    <row r="7" spans="1:9" ht="16.5">
       <c r="A7">
         <v>6</v>
       </c>
@@ -665,8 +665,11 @@
       <c r="H7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="16.5">
+      <c r="I7">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="16.5">
       <c r="A8">
         <v>7</v>
       </c>
@@ -685,8 +688,11 @@
       <c r="H8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="16.5">
+      <c r="I8">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="16.5">
       <c r="A9">
         <v>8</v>
       </c>
@@ -705,8 +711,11 @@
       <c r="H9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="16.5">
+      <c r="I9">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="16.5">
       <c r="A10">
         <v>9</v>
       </c>
@@ -726,7 +735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="16.5">
+    <row r="16" spans="1:9" ht="16.5">
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>

--- a/Linear Regulator/Book1.xlsx
+++ b/Linear Regulator/Book1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qche619\Downloads\ELECTENG-311-Teamwork\Linear Regulator\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qche619\Documents\GitHub\ELECTENG-311-Teamwork\Linear Regulator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41D5467-8EBA-4764-B4C7-2A7C42B6BF3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25E1EB4B-6CA7-4351-AF59-8A99A788C845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D829F5A1-D388-437B-AA51-65B45AF8D5F5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="65">
   <si>
     <t>Purpose</t>
   </si>
@@ -126,6 +126,115 @@
   </si>
   <si>
     <t>RES 3.9kR 1608 SM</t>
+  </si>
+  <si>
+    <t>CAP 10uF 16V ELE SM</t>
+  </si>
+  <si>
+    <t>CAP CER 100nF 25V X7R SM0603</t>
+  </si>
+  <si>
+    <t>HEADER POLARISED 2WAY TH</t>
+  </si>
+  <si>
+    <t>MOSFET P-CH 55V 12A TO-220A</t>
+  </si>
+  <si>
+    <t>RES CER 47K 1608 SM</t>
+  </si>
+  <si>
+    <t>Dual 10pA 33V/us 11MHz SOIC-8 Operational Amplifier ROHS</t>
+  </si>
+  <si>
+    <t>Dual commercial grade standard comparator 8-SOIC -40 to 85</t>
+  </si>
+  <si>
+    <t>399-7845-2-ND</t>
+  </si>
+  <si>
+    <t>493-2173-2-ND</t>
+  </si>
+  <si>
+    <t>ECE-CAPAE4X5.4SM</t>
+  </si>
+  <si>
+    <t>CAP000303</t>
+  </si>
+  <si>
+    <t>CAP000624</t>
+  </si>
+  <si>
+    <t>CAP000618</t>
+  </si>
+  <si>
+    <t>CAP000530</t>
+  </si>
+  <si>
+    <t>CAP000520</t>
+  </si>
+  <si>
+    <t>TRA000011</t>
+  </si>
+  <si>
+    <t>RES000102</t>
+  </si>
+  <si>
+    <t>RES000138</t>
+  </si>
+  <si>
+    <t>RES000145</t>
+  </si>
+  <si>
+    <t>RES000150</t>
+  </si>
+  <si>
+    <t>RES000158</t>
+  </si>
+  <si>
+    <t>Texas Instruments </t>
+  </si>
+  <si>
+    <t>TLV9162IDR</t>
+  </si>
+  <si>
+    <t>296-TLV9162IDRCT-ND</t>
+  </si>
+  <si>
+    <t>8-SOIC</t>
+  </si>
+  <si>
+    <t>ECE-RESC2012-0805SM</t>
+  </si>
+  <si>
+    <t>N08E_TEX</t>
+  </si>
+  <si>
+    <t>296-1398-5-ND</t>
+  </si>
+  <si>
+    <t>LM393A</t>
+  </si>
+  <si>
+    <t>IRF9Z24NPBF-ND</t>
+  </si>
+  <si>
+    <t>TO220AB</t>
+  </si>
+  <si>
+    <t>Electus</t>
+  </si>
+  <si>
+    <t>HM3412</t>
+  </si>
+  <si>
+    <t>IRF9Z24N</t>
+  </si>
+  <si>
+    <t>ECE-600102STTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+CON000001</t>
   </si>
 </sst>
 </file>
@@ -148,18 +257,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF605E5C"/>
-      <name val="Aptos Narrow"/>
+      <name val="Segoe UI"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -174,10 +287,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -512,18 +634,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FE5874B-1229-449E-B35A-29CF6E1C6CD6}">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="10.25" customWidth="1"/>
     <col min="3" max="3" width="16.5" customWidth="1"/>
-    <col min="4" max="4" width="27.25" customWidth="1"/>
+    <col min="4" max="4" width="55.5" customWidth="1"/>
     <col min="5" max="5" width="24.625" customWidth="1"/>
     <col min="6" max="6" width="17.125" customWidth="1"/>
     <col min="7" max="7" width="24.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:8">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -546,200 +668,375 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16.5">
+    <row r="2" spans="1:8" ht="16.5">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="F2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="16.5">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="F3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16.5">
+    <row r="4" spans="1:8" ht="16.5">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="C4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="F4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16.5">
+    <row r="5" spans="1:8" ht="16.5">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="C5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="1" t="s">
+      <c r="F5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="16.5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="16.5">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="C6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" s="1" t="s">
+      <c r="F6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16.5">
+    <row r="7" spans="1:8" ht="16.5">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>17</v>
+      <c r="C7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="16.5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="16.5">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>14</v>
+      <c r="C8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="H8">
         <v>2</v>
       </c>
-      <c r="I8">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="16.5">
+    </row>
+    <row r="9" spans="1:8" ht="16.5">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="C9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G9" s="1" t="s">
+      <c r="F9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H9">
         <v>1</v>
       </c>
-      <c r="I9">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="16.5">
+    </row>
+    <row r="10" spans="1:8" ht="16.5">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="C10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="16.5">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="16.5">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" s="1" t="s">
+      <c r="F12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="16.5">
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
+      <c r="H12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="16.5">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G13" s="3"/>
+      <c r="H13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="16.5">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="16.5">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="16.5">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="33">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="16.5">
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
